--- a/Mentorias/2026-09-16_Emerson_e_Julio/18_Comparativo_Top10_Acoes.xlsx
+++ b/Mentorias/2026-09-16_Emerson_e_Julio/18_Comparativo_Top10_Acoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\mestrado\coleta_dados_petr4\Mentorias\2026-09-16_Emerson_e_Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44038699-C29F-4EC1-8DBD-1417543DC80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59228422-7208-4BB3-B8B4-62207BCCB7FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="105">
   <si>
     <t>Comparativo — as 10 principais ações do Ibovespa</t>
   </si>
@@ -223,7 +223,7 @@
     <t>Preço de fechamento em 2026-09-15</t>
   </si>
   <si>
-    <t>Investidores — total (2026-12-31)</t>
+    <t>Investidores — total (assembleia de 2026-04-30)</t>
   </si>
   <si>
     <t xml:space="preserve">  dos quais pessoa física</t>
@@ -335,15 +335,27 @@
     <t>ITUB4 — ITAU UNIBANCO HOLDING S.A.</t>
   </si>
   <si>
+    <t>Investidores — total (assembleia de 2026-05-19)</t>
+  </si>
+  <si>
     <t>PETR4 — PETROLEO BRASILEIRO S.A. PETROBRAS</t>
   </si>
   <si>
+    <t>Investidores — total (assembleia de 2026-04-16)</t>
+  </si>
+  <si>
     <t>SBSP3 — CIA SANEAMENTO BASICO EST SAO PAULO</t>
   </si>
   <si>
+    <t>Investidores — total (assembleia de 2026-04-28)</t>
+  </si>
+  <si>
     <t>BBDC4 — BCO BRADESCO S.A.</t>
   </si>
   <si>
+    <t>Investidores — total (assembleia de 2026-05-08)</t>
+  </si>
+  <si>
     <t>B3SA3 — B3 S.A. - BRASIL, BOLSA, BALCÃO</t>
   </si>
   <si>
@@ -356,7 +368,13 @@
     <t>BBAS3 — BCO BRASIL S.A.</t>
   </si>
   <si>
+    <t>Investidores — total (assembleia de 2026-04-29)</t>
+  </si>
+  <si>
     <t>ABEV3 — AMBEV S.A.</t>
+  </si>
+  <si>
+    <t>Investidores — total (assembleia de 2026-08-13)</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1221,7 @@
         <v>294151</v>
       </c>
       <c r="F12" s="16">
-        <v>16950.099999999999</v>
+        <v>16903.099999999999</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>36</v>
@@ -1427,7 +1445,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -1453,7 +1471,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B5" s="23">
         <v>1551254</v>
@@ -2017,7 +2035,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -2043,7 +2061,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="B5" s="23">
         <v>213087</v>
@@ -3223,7 +3241,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="B5" s="23">
         <v>667798</v>
@@ -3787,7 +3805,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -3813,7 +3831,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="B5" s="23">
         <v>1183775</v>
@@ -4377,7 +4395,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -4403,7 +4421,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="B5" s="23">
         <v>60606</v>
@@ -4967,7 +4985,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -4993,7 +5011,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="B5" s="23">
         <v>882476</v>
@@ -5557,7 +5575,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -5618,7 +5636,7 @@
         <v>59</v>
       </c>
       <c r="B9" s="23">
-        <v>4985893391</v>
+        <v>4972065060</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5626,7 +5644,7 @@
         <v>60</v>
       </c>
       <c r="B10" s="23">
-        <v>16950.099999999999</v>
+        <v>16903.099999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6147,7 +6165,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -6737,7 +6755,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
